--- a/04_arquitectura/entrega_2/tablas/arquitectura_fisica_BI_Analitica.xlsx
+++ b/04_arquitectura/entrega_2/tablas/arquitectura_fisica_BI_Analitica.xlsx
@@ -551,7 +551,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Celery workers (Django) + Redshift SQL</t>
+          <t>Trabajos de Laravel + Redshift SQL</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Celery Beat + SES (correo) + S3 (almacenamiento PDF/XLSX)</t>
+          <t>Planificador de Laravel + SES (correo) + S3 (almacenamiento PDF/XLSX)</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>CloudWatch + SNS + Celery</t>
+          <t>CloudWatch + SNS + trabajos de Laravel</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
